--- a/src/main/webapp/xlsxTemplates/基础物料信息导入示例.xlsx
+++ b/src/main/webapp/xlsxTemplates/基础物料信息导入示例.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>物料编号</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>个</t>
+  </si>
+  <si>
+    <t>10为原材料，20为成品，30为半成品，40为低值易耗品，50为其他</t>
   </si>
   <si>
     <t>紧固件</t>
@@ -1062,6 +1065,9 @@
   <sheetPr/>
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="4" max="4" width="54.8083333333333" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
@@ -1117,20 +1123,20 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2">
-        <v>10</v>
+      <c r="D2" t="s">
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>0.02</v>
@@ -1142,13 +1148,13 @@
         <v>0.45</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/webapp/xlsxTemplates/基础物料信息导入示例.xlsx
+++ b/src/main/webapp/xlsxTemplates/基础物料信息导入示例.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>序号</t>
+  </si>
   <si>
     <t>物料编号</t>
   </si>
@@ -114,10 +117,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -585,138 +595,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1063,13 +1074,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="4" max="4" width="54.8083333333333" customWidth="1"/>
+    <col min="4" max="4" width="14.7833333333333" customWidth="1"/>
+    <col min="5" max="5" width="57.825" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1112,10 +1124,13 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -1126,7 +1141,7 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F2" t="s">
@@ -1138,23 +1153,26 @@
       <c r="H2" t="s">
         <v>21</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2">
         <v>0.02</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.5</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.45</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
       </c>
       <c r="N2" t="s">
         <v>24</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
